--- a/simulacaoes_/custo_robustez_C13/simulacao_rho025/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/custo_robustez_C13/simulacao_rho025/pre_sizing_results_optimized.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,67 +417,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>d_cm</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>esp_cm</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>bw_cm</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>h_cm</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>esp_tab_cm</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>of_volume_m3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>of_fator_flecha</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longarina_g_m</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>longarina_g_v</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longarina_g_f</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>tabuleiro_g_m</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>longarina_g_esp</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>tabuleiro_g_esp</t>
         </is>
@@ -497,2052 +485,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>45.55023955094016</v>
+        <v>46.66464794052497</v>
       </c>
       <c r="B2" t="n">
-        <v>98.66749013935753</v>
+        <v>76.06580270504223</v>
       </c>
       <c r="C2" t="n">
-        <v>45.73254413978409</v>
+        <v>45.5021508391111</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6011915352433</v>
+        <v>7.601702229146588</v>
       </c>
       <c r="E2" t="n">
-        <v>2.097400442892014</v>
+        <v>3.423309216529636</v>
       </c>
       <c r="F2" t="n">
-        <v>4.810149990699219</v>
+        <v>4.977071486191043</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3358989883711284</v>
+        <v>0.3036606078871977</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.001220494068898958</v>
+        <v>-0.004700614475703862</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5493946261519641</v>
+        <v>-0.5505484754990617</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2202171903562903</v>
+        <v>-0.2240737122783162</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.004658057623777335</v>
+        <v>-0.0001169595021486758</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5530623387969162</v>
+        <v>-0.5533202116134124</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02623043918076513</v>
+        <v>-0.0004779642469125711</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99.99999999994907</v>
+        <v>99.99999998428996</v>
       </c>
       <c r="B3" t="n">
-        <v>105.8180449235911</v>
+        <v>183.0515805021668</v>
       </c>
       <c r="C3" t="n">
-        <v>45.62391812980413</v>
+        <v>45.50352607017343</v>
       </c>
       <c r="D3" t="n">
-        <v>6.30441090498767</v>
+        <v>6.630838797474711</v>
       </c>
       <c r="E3" t="n">
-        <v>2.927008608876601</v>
+        <v>3.323825461647302</v>
       </c>
       <c r="F3" t="n">
-        <v>13.02953950562582</v>
+        <v>13.13874190465617</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02086564870495635</v>
+        <v>0.02072888853213596</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8966832535345791</v>
+        <v>-0.8897864263840449</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9337502508771245</v>
+        <v>-0.9296269635740947</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9613473940276475</v>
+        <v>-0.9579160423203587</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0104799153868966</v>
+        <v>-3.246965760093997e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6235034864966368</v>
+        <v>-0.6062499998851203</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.002151766429771212</v>
+        <v>-0.0007835711496516351</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>57.7411273521081</v>
+        <v>63.08637874607889</v>
       </c>
       <c r="B4" t="n">
-        <v>165.4733431379681</v>
+        <v>104.0790833290081</v>
       </c>
       <c r="C4" t="n">
-        <v>45.62223944904563</v>
+        <v>45.60965374033835</v>
       </c>
       <c r="D4" t="n">
-        <v>11.088124567317</v>
+        <v>10.95925772157845</v>
       </c>
       <c r="E4" t="n">
-        <v>2.465995047768416</v>
+        <v>3.310822007755035</v>
       </c>
       <c r="F4" t="n">
-        <v>6.188017184487595</v>
+        <v>6.938014613516325</v>
       </c>
       <c r="G4" t="n">
-        <v>0.147715048704051</v>
+        <v>0.1054246492794919</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4954953817720542</v>
+        <v>-0.5837384036665492</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7354418353791025</v>
+        <v>-0.7737314238471286</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6840167432024072</v>
+        <v>-0.7552889911529626</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.009399643512036154</v>
+        <v>-0.0482336824012264</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3071943513732124</v>
+        <v>-0.3363191445807019</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.001779660295661721</v>
+        <v>-0.0243674978529676</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>55.855252438932</v>
+        <v>55.50126836797912</v>
       </c>
       <c r="B5" t="n">
-        <v>129.3410441234301</v>
+        <v>136.4269007818278</v>
       </c>
       <c r="C5" t="n">
-        <v>45.76157013478146</v>
+        <v>45.5002143634075</v>
       </c>
       <c r="D5" t="n">
-        <v>11.18951948603886</v>
+        <v>11.38149765436035</v>
       </c>
       <c r="E5" t="n">
-        <v>2.589567819235323</v>
+        <v>4.128726929129954</v>
       </c>
       <c r="F5" t="n">
-        <v>5.964419713277004</v>
+        <v>5.959372527779067</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1674055674343378</v>
+        <v>0.1701060720547944</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4436545863426174</v>
+        <v>-0.3932978151125107</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7137509440816675</v>
+        <v>-0.6931470557054951</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6401571217497115</v>
+        <v>-0.596351574610785</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0008145135214110216</v>
+        <v>-0.003132178294050693</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2930785118971168</v>
+        <v>-0.2808530249408473</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.03266450994284827</v>
+        <v>-4.763631277646119e-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>46.22494610962817</v>
+        <v>65.04788560917112</v>
       </c>
       <c r="B6" t="n">
-        <v>108.730153046443</v>
+        <v>111.0721546257308</v>
       </c>
       <c r="C6" t="n">
-        <v>45.71230117345365</v>
+        <v>45.51581812845622</v>
       </c>
       <c r="D6" t="n">
-        <v>7.532078895087407</v>
+        <v>11.37520734230054</v>
       </c>
       <c r="E6" t="n">
-        <v>2.579918025228057</v>
+        <v>2.351532875283419</v>
       </c>
       <c r="F6" t="n">
-        <v>4.892141536538238</v>
+        <v>7.314680778042591</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3175347777324752</v>
+        <v>0.09451311724011309</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.04379093472201213</v>
+        <v>-0.6191016852159245</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5643494874388135</v>
+        <v>-0.7895932535026681</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.264105084039868</v>
+        <v>-0.7824492750890215</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.006405532466650033</v>
+        <v>-0.1435923655433843</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5575514073439418</v>
+        <v>-0.3506626635170638</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.02174326560355251</v>
+        <v>-0.003515139656938837</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>54.57553208157768</v>
+        <v>58.30169585706076</v>
       </c>
       <c r="B7" t="n">
-        <v>113.6302840442653</v>
+        <v>111.6234833697728</v>
       </c>
       <c r="C7" t="n">
-        <v>45.62968641132358</v>
+        <v>45.5034187782863</v>
       </c>
       <c r="D7" t="n">
-        <v>11.2046236479751</v>
+        <v>11.2039332505114</v>
       </c>
       <c r="E7" t="n">
-        <v>2.589722971837608</v>
+        <v>3.720651550955761</v>
       </c>
       <c r="F7" t="n">
-        <v>5.832387392946071</v>
+        <v>6.298633602088351</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1822489960495012</v>
+        <v>0.1413450922415931</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4046674731535094</v>
+        <v>-0.4752420782727124</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6978745752391895</v>
+        <v>-0.726850563455218</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6063264463165534</v>
+        <v>-0.6671455756801469</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.004299219178724384</v>
+        <v>-0.01417087434345628</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2945158301751096</v>
+        <v>-0.3013311509547568</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.00343039723898455</v>
+        <v>-0.0007597285080682137</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>62.55681828697039</v>
+        <v>93.75244992575831</v>
       </c>
       <c r="B8" t="n">
-        <v>111.412703513385</v>
+        <v>102.2509411257177</v>
       </c>
       <c r="C8" t="n">
-        <v>45.62391812980413</v>
+        <v>45.5492863653511</v>
       </c>
       <c r="D8" t="n">
-        <v>10.72278685066325</v>
+        <v>7.506225151365776</v>
       </c>
       <c r="E8" t="n">
-        <v>2.354476740818509</v>
+        <v>3.842659187023934</v>
       </c>
       <c r="F8" t="n">
-        <v>6.793010937148241</v>
+        <v>11.89347589256228</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1094978888545017</v>
+        <v>0.02571525072249446</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6012810820936626</v>
+        <v>-0.8677355478877971</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7816672881343026</v>
+        <v>-0.9164727199954286</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7688363649968627</v>
+        <v>-0.9464488831816942</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.02273995256695764</v>
+        <v>-0.009090342219195132</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3432399659195776</v>
+        <v>-0.5605647900821076</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.002151766429771212</v>
+        <v>-0.01095252563357837</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>87.83327061563764</v>
+        <v>82.87808080246586</v>
       </c>
       <c r="B9" t="n">
-        <v>109.4796208712797</v>
+        <v>112.4329983970023</v>
       </c>
       <c r="C9" t="n">
-        <v>45.61813262468851</v>
+        <v>47.72167282905626</v>
       </c>
       <c r="D9" t="n">
-        <v>8.575266364139695</v>
+        <v>9.026824129176797</v>
       </c>
       <c r="E9" t="n">
-        <v>2.604579160763389</v>
+        <v>3.75925867158172</v>
       </c>
       <c r="F9" t="n">
-        <v>10.81329065775502</v>
+        <v>10.03057457470579</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03242891806190244</v>
+        <v>0.0394211437311641</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8507448102040648</v>
+        <v>-0.8116820447982329</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9066098852274889</v>
+        <v>-0.884850710974737</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9371425924500102</v>
+        <v>-0.9145202242065701</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1427759329487581</v>
+        <v>-0.1024340554004408</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5324350928624086</v>
+        <v>-0.4810459658680316</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0008693177381191232</v>
+        <v>-0.2657373171909687</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>50.59230374668575</v>
+        <v>48.39602733855109</v>
       </c>
       <c r="B10" t="n">
-        <v>86.25072844585496</v>
+        <v>106.5721381165446</v>
       </c>
       <c r="C10" t="n">
-        <v>45.62223377523774</v>
+        <v>45.70011592923651</v>
       </c>
       <c r="D10" t="n">
-        <v>7.020392069481131</v>
+        <v>7.498579451979216</v>
       </c>
       <c r="E10" t="n">
-        <v>2.034564735052606</v>
+        <v>3.472671051206147</v>
       </c>
       <c r="F10" t="n">
-        <v>5.445738869502713</v>
+        <v>5.221167388830489</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2252547042297897</v>
+        <v>0.2645057160137572</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2678666484305852</v>
+        <v>-0.1063559471858283</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6464614551252942</v>
+        <v>-0.5865949870839802</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4840102763603332</v>
+        <v>-0.3276175891968024</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.007383552738098518</v>
+        <v>-0.02882752120617929</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5866090288383149</v>
+        <v>-0.5645741777005822</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.001778402606426378</v>
+        <v>-0.04447020649700345</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>65.96097980665076</v>
+        <v>81.51681767689544</v>
       </c>
       <c r="B11" t="n">
-        <v>165.727887840186</v>
+        <v>158.253729478562</v>
       </c>
       <c r="C11" t="n">
-        <v>45.62305399064618</v>
+        <v>45.96040755340699</v>
       </c>
       <c r="D11" t="n">
-        <v>10.88165786130298</v>
+        <v>9.140620574093509</v>
       </c>
       <c r="E11" t="n">
-        <v>2.998471500260174</v>
+        <v>3.749956104004253</v>
       </c>
       <c r="F11" t="n">
-        <v>7.339007586378111</v>
+        <v>9.718926166377656</v>
       </c>
       <c r="G11" t="n">
-        <v>0.09029935759431094</v>
+        <v>0.04169541384884653</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6583059937633152</v>
+        <v>-0.8025898904440719</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8078270177059614</v>
+        <v>-0.8799828514825507</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8116266043352043</v>
+        <v>-0.9090237922029852</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1070825906707597</v>
+        <v>-0.06057579490914434</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.368720233580375</v>
+        <v>-0.4710917292622979</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.001960216321289724</v>
+        <v>-0.1023127896459973</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>48.44083004036247</v>
+        <v>91.67382782336819</v>
       </c>
       <c r="B12" t="n">
-        <v>91.36712094289882</v>
+        <v>76.06945729041939</v>
       </c>
       <c r="C12" t="n">
-        <v>45.61522782964136</v>
+        <v>45.5021457708287</v>
       </c>
       <c r="D12" t="n">
-        <v>7.282129935597058</v>
+        <v>8.042018912410752</v>
       </c>
       <c r="E12" t="n">
-        <v>3.047339843320116</v>
+        <v>2.042508211591567</v>
       </c>
       <c r="F12" t="n">
-        <v>5.165813683691488</v>
+        <v>11.54751713618328</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2656100798577603</v>
+        <v>0.02777521419949316</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1675435144757426</v>
+        <v>-0.8589872959270025</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.60894013290784</v>
+        <v>-0.9113618051328298</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3879623586748348</v>
+        <v>-0.9417131370246766</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.007107132746231602</v>
+        <v>-0.07437107398516088</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5722944904357404</v>
+        <v>-0.5453648659583799</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0002254239841100699</v>
+        <v>-0.0004768379619311813</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>92.02930685553872</v>
+        <v>50.70821509085468</v>
       </c>
       <c r="B13" t="n">
-        <v>129.4769410141414</v>
+        <v>95.75994042741826</v>
       </c>
       <c r="C13" t="n">
-        <v>45.68136280821901</v>
+        <v>45.60508505184268</v>
       </c>
       <c r="D13" t="n">
-        <v>7.519651597040778</v>
+        <v>7.143836126072127</v>
       </c>
       <c r="E13" t="n">
-        <v>2.169235830279051</v>
+        <v>2.393197261283362</v>
       </c>
       <c r="F13" t="n">
-        <v>11.48455695156752</v>
+        <v>5.505103489021465</v>
       </c>
       <c r="G13" t="n">
-        <v>0.02757658576929147</v>
+        <v>0.22149574375685</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8693851490380592</v>
+        <v>-0.2216663833362945</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9174443514842634</v>
+        <v>-0.6289608649989338</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9473144685642013</v>
+        <v>-0.4404572765203369</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.03134655016364363</v>
+        <v>-0.004490804454191699</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5638425704127467</v>
+        <v>-0.5796033980905555</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.01488528773920021</v>
+        <v>-0.02335223374281825</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>68.07645947717401</v>
+        <v>79.06108017865972</v>
       </c>
       <c r="B14" t="n">
-        <v>113.5779227185407</v>
+        <v>99.38745053486488</v>
       </c>
       <c r="C14" t="n">
-        <v>45.69320997542498</v>
+        <v>45.92817931286216</v>
       </c>
       <c r="D14" t="n">
-        <v>10.11679725138299</v>
+        <v>10.01749154738858</v>
       </c>
       <c r="E14" t="n">
-        <v>2.591644633868764</v>
+        <v>3.420845689323817</v>
       </c>
       <c r="F14" t="n">
-        <v>7.518024784892749</v>
+        <v>9.434261893770511</v>
       </c>
       <c r="G14" t="n">
-        <v>0.08009422666244953</v>
+        <v>0.04661041763753525</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6887001326466023</v>
+        <v>-0.7841726316920585</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8223568946782779</v>
+        <v>-0.8701301530370354</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.8335703530659934</v>
+        <v>-0.8975923963572252</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.009158992191819195</v>
+        <v>-0.1706753004526716</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.3845546726703771</v>
+        <v>-0.4531341488064492</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.01751139968266148</v>
+        <v>-0.0951509584138141</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>79.30391383169169</v>
+        <v>47.91522460779832</v>
       </c>
       <c r="B15" t="n">
-        <v>95.87611054516316</v>
+        <v>106.6011732641646</v>
       </c>
       <c r="C15" t="n">
-        <v>41.68992185938563</v>
+        <v>45.50320223038107</v>
       </c>
       <c r="D15" t="n">
-        <v>9.734544270058153</v>
+        <v>7.495698074407341</v>
       </c>
       <c r="E15" t="n">
-        <v>2.58373469193819</v>
+        <v>3.374255986336454</v>
       </c>
       <c r="F15" t="n">
-        <v>9.388659855061036</v>
+        <v>5.141194392090669</v>
       </c>
       <c r="G15" t="n">
-        <v>0.04641745087972149</v>
+        <v>0.2746021113419701</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7998498206271806</v>
+        <v>-0.07965169853778339</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8784736927131163</v>
+        <v>-0.5770300027512997</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.9073050271659298</v>
+        <v>-0.3007904385296966</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.08032840462500257</v>
+        <v>-0.009411545340467075</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.4685925599588032</v>
+        <v>-0.5614489599506891</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1488180942607656</v>
+        <v>-0.0007116067513475433</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>47.7515819505147</v>
+        <v>95.82832537509643</v>
       </c>
       <c r="B16" t="n">
-        <v>108.1283383008181</v>
+        <v>110.7571276746862</v>
       </c>
       <c r="C16" t="n">
-        <v>45.62362572316846</v>
+        <v>45.60221814653638</v>
       </c>
       <c r="D16" t="n">
-        <v>7.340428116052436</v>
+        <v>7.594511043020246</v>
       </c>
       <c r="E16" t="n">
-        <v>2.164579646962616</v>
+        <v>3.383829604022394</v>
       </c>
       <c r="F16" t="n">
-        <v>5.074306054720294</v>
+        <v>12.37701651843791</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2804620805499329</v>
+        <v>0.02392384708654863</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1315181300944104</v>
+        <v>-0.8756445806711557</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.595783313993424</v>
+        <v>-0.9211107876807614</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3525028280972264</v>
+        <v>-0.9506353004447842</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.0008687515699673044</v>
+        <v>-0.1015102743982452</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5677086717840741</v>
+        <v>-0.5757446293053925</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.002086949875321168</v>
+        <v>-0.02271514367474955</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>85.75926913879303</v>
+        <v>59.36591033951475</v>
       </c>
       <c r="B17" t="n">
-        <v>169.2127078305691</v>
+        <v>103.9770961093313</v>
       </c>
       <c r="C17" t="n">
-        <v>45.6230942362966</v>
+        <v>45.50856108580179</v>
       </c>
       <c r="D17" t="n">
-        <v>8.613835473860957</v>
+        <v>10.95844589537991</v>
       </c>
       <c r="E17" t="n">
-        <v>2.047743709668185</v>
+        <v>3.37543327026282</v>
       </c>
       <c r="F17" t="n">
-        <v>10.39886915782814</v>
+        <v>6.396145415648903</v>
       </c>
       <c r="G17" t="n">
-        <v>0.03518826825016276</v>
+        <v>0.131903158492413</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8402414583243004</v>
+        <v>-0.5082709888572742</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9006715585880607</v>
+        <v>-0.742198440500776</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.931229401610996</v>
+        <v>-0.6955940780854584</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.09612884180038542</v>
+        <v>-0.01097307253041895</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5169111194982271</v>
+        <v>-0.3202443275463607</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.001969137406085828</v>
+        <v>-0.001902463511511132</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>60.33249550573269</v>
+        <v>76.90730140205406</v>
       </c>
       <c r="B18" t="n">
-        <v>169.5898493346789</v>
+        <v>144.6737221912496</v>
       </c>
       <c r="C18" t="n">
-        <v>45.61545260567927</v>
+        <v>45.5072455475508</v>
       </c>
       <c r="D18" t="n">
-        <v>11.15037638244956</v>
+        <v>9.665791263883543</v>
       </c>
       <c r="E18" t="n">
-        <v>2.619560267069514</v>
+        <v>3.399506895723941</v>
       </c>
       <c r="F18" t="n">
-        <v>6.55953510123382</v>
+        <v>8.947516577375271</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1255574420577841</v>
+        <v>0.05122482020735317</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5563791498993808</v>
+        <v>-0.766450811306266</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7616416348719892</v>
+        <v>-0.8609778004027081</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7336107630815776</v>
+        <v>-0.8863297316966439</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.06096457558379045</v>
+        <v>-0.05718770090004976</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.3265908323510659</v>
+        <v>-0.4373846415025203</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0002752491471619952</v>
+        <v>-0.001610121677955295</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>51.8036425224556</v>
+        <v>47.42079134968911</v>
       </c>
       <c r="B19" t="n">
-        <v>85.67490193541562</v>
+        <v>100.1731380584462</v>
       </c>
       <c r="C19" t="n">
-        <v>45.61721607394712</v>
+        <v>46.37306582618535</v>
       </c>
       <c r="D19" t="n">
-        <v>7.020392069481131</v>
+        <v>7.537560658539642</v>
       </c>
       <c r="E19" t="n">
-        <v>2.034564735052606</v>
+        <v>3.389476140390656</v>
       </c>
       <c r="F19" t="n">
-        <v>5.639669787713817</v>
+        <v>5.105228189755172</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2061670095445887</v>
+        <v>0.2858798822658976</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3171294342394697</v>
+        <v>-0.0507868005208663</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6653776445365668</v>
+        <v>-0.5667318823013807</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5296109628245037</v>
+        <v>-0.2714457484931813</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.04973123342539772</v>
+        <v>-0.02414034480618728</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5946685070338062</v>
+        <v>-0.5582351437729793</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0006661497734139359</v>
+        <v>-0.1940146280411897</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>51.16428272649124</v>
+        <v>61.97876329456743</v>
       </c>
       <c r="B20" t="n">
-        <v>107.6198979515976</v>
+        <v>137.9618008715611</v>
       </c>
       <c r="C20" t="n">
-        <v>45.62286078082985</v>
+        <v>45.51906061579479</v>
       </c>
       <c r="D20" t="n">
-        <v>7.152362747569894</v>
+        <v>10.90457472139721</v>
       </c>
       <c r="E20" t="n">
-        <v>2.643327865724849</v>
+        <v>2.119978093141255</v>
       </c>
       <c r="F20" t="n">
-        <v>5.563913225329476</v>
+        <v>6.759150987149666</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2161218169646727</v>
+        <v>0.1124531972723665</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2915969697316259</v>
+        <v>-0.5616533407408891</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6555063048131132</v>
+        <v>-0.7639757972986562</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5060869277193993</v>
+        <v>-0.737917074908972</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.06294626159893936</v>
+        <v>-0.01897923465228548</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5904146133768697</v>
+        <v>-0.3282197065915243</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.001917388310387568</v>
+        <v>-0.0042356923988425</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>64.39920702519525</v>
+        <v>74.84366292312313</v>
       </c>
       <c r="B21" t="n">
-        <v>130.3478812053766</v>
+        <v>103.0258018735222</v>
       </c>
       <c r="C21" t="n">
-        <v>45.78789192606066</v>
+        <v>46.59051142311048</v>
       </c>
       <c r="D21" t="n">
-        <v>10.44145507056237</v>
+        <v>10.1277597068354</v>
       </c>
       <c r="E21" t="n">
-        <v>3.071624426572307</v>
+        <v>3.353885357183354</v>
       </c>
       <c r="F21" t="n">
-        <v>7.017485609468582</v>
+        <v>8.722557525339493</v>
       </c>
       <c r="G21" t="n">
-        <v>0.09826311493478422</v>
+        <v>0.05663146497953984</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6338428848714206</v>
+        <v>-0.7470867187141094</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7965358320876272</v>
+        <v>-0.8510182525188505</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.793566358650602</v>
+        <v>-0.8736482348347236</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.006015736429568347</v>
+        <v>-0.1232735487581893</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3570303098600192</v>
+        <v>-0.422294285125338</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0384991511908206</v>
+        <v>-0.2423358718023312</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>84.87090458710631</v>
+        <v>49.05831046020506</v>
       </c>
       <c r="B22" t="n">
-        <v>83.71357677373707</v>
+        <v>106.5721381165446</v>
       </c>
       <c r="C22" t="n">
-        <v>45.79168870382271</v>
+        <v>45.50320223038107</v>
       </c>
       <c r="D22" t="n">
-        <v>8.555449518621218</v>
+        <v>7.498337581033714</v>
       </c>
       <c r="E22" t="n">
-        <v>2.047743709668185</v>
+        <v>3.372735749553137</v>
       </c>
       <c r="F22" t="n">
-        <v>10.21548173776869</v>
+        <v>5.315856190507954</v>
       </c>
       <c r="G22" t="n">
-        <v>0.03646088367544157</v>
+        <v>0.2512579813938927</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8354368795093051</v>
+        <v>-0.1415405302796553</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8979877953667542</v>
+        <v>-0.5993370160349953</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9284822803556927</v>
+        <v>-0.362577797786484</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.06359002070613058</v>
+        <v>-0.04454422345747661</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5102616798560483</v>
+        <v>-0.568879017991333</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.03934076701798285</v>
+        <v>-0.0007116067513475433</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>93.86412208575973</v>
+        <v>60.33033905950946</v>
       </c>
       <c r="B23" t="n">
-        <v>80.86735507632807</v>
+        <v>104.0288933391805</v>
       </c>
       <c r="C23" t="n">
-        <v>45.84845595497956</v>
+        <v>45.50809761071766</v>
       </c>
       <c r="D23" t="n">
-        <v>7.512824512570933</v>
+        <v>10.9317399072749</v>
       </c>
       <c r="E23" t="n">
-        <v>2.535734963163254</v>
+        <v>4.065383734215501</v>
       </c>
       <c r="F23" t="n">
-        <v>11.88908694886961</v>
+        <v>6.526651315618683</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02582126325476837</v>
+        <v>0.1242369054895349</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8764533867186343</v>
+        <v>-0.5309673515737312</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9216014720905653</v>
+        <v>-0.7519000812703203</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9510460950360909</v>
+        <v>-0.7141034817083779</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.09597958310579884</v>
+        <v>-0.009592100728319588</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5775762263817291</v>
+        <v>-0.3218215736594919</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.05192412586391283</v>
+        <v>-0.00179946904837025</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>61.53000867724289</v>
+        <v>69.96107535311369</v>
       </c>
       <c r="B24" t="n">
-        <v>129.397284571111</v>
+        <v>115.4522452921147</v>
       </c>
       <c r="C24" t="n">
-        <v>45.66648226168225</v>
+        <v>45.50179660551004</v>
       </c>
       <c r="D24" t="n">
-        <v>10.72189323664217</v>
+        <v>10.14898016055068</v>
       </c>
       <c r="E24" t="n">
-        <v>2.162069413771294</v>
+        <v>2.083921616038802</v>
       </c>
       <c r="F24" t="n">
-        <v>6.645349536902161</v>
+        <v>7.844344042826993</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1163847534000719</v>
+        <v>0.07196016692306119</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5815053055277842</v>
+        <v>-0.6925698488050793</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7728159747997766</v>
+        <v>-0.824191595094678</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7534972075310817</v>
+        <v>-0.836356068436697</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.006061319558431889</v>
+        <v>-0.01565587912823639</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.3355542601910808</v>
+        <v>-0.3865903635196438</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.01158677930203441</v>
+        <v>-0.0003992456688980961</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>47.43912211518776</v>
+        <v>72.63008427085872</v>
       </c>
       <c r="B25" t="n">
-        <v>109.195705196674</v>
+        <v>118.6548956526697</v>
       </c>
       <c r="C25" t="n">
-        <v>45.6288576485721</v>
+        <v>45.51098808268288</v>
       </c>
       <c r="D25" t="n">
-        <v>7.375030221434423</v>
+        <v>10.72430244403342</v>
       </c>
       <c r="E25" t="n">
-        <v>2.596877543901453</v>
+        <v>2.083921616038802</v>
       </c>
       <c r="F25" t="n">
-        <v>5.035038353145423</v>
+        <v>8.410946312029594</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2875635162355777</v>
+        <v>0.06316079286716958</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1144825614972743</v>
+        <v>-0.723959915453751</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5896134202869699</v>
+        <v>-0.8394138574860924</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.3355609742971485</v>
+        <v>-0.8580956637743921</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.0003953747043247008</v>
+        <v>-0.1627371184752788</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5656297626628963</v>
+        <v>-0.4061074912306544</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.003246688870384483</v>
+        <v>-0.002441796151750053</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>76.05570249507265</v>
+        <v>66.67843230730736</v>
       </c>
       <c r="B26" t="n">
-        <v>129.4895518067116</v>
+        <v>122.7853069011509</v>
       </c>
       <c r="C26" t="n">
-        <v>45.76137012199645</v>
+        <v>46.64960899844169</v>
       </c>
       <c r="D26" t="n">
-        <v>9.61343236228466</v>
+        <v>10.26401878287147</v>
       </c>
       <c r="E26" t="n">
-        <v>2.402826564870957</v>
+        <v>3.380814132447288</v>
       </c>
       <c r="F26" t="n">
-        <v>8.76722256441985</v>
+        <v>7.392492144958691</v>
       </c>
       <c r="G26" t="n">
-        <v>0.05372221778295742</v>
+        <v>0.08583088132850408</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.7743105542507925</v>
+        <v>-0.6461887253876564</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8650569627732501</v>
+        <v>-0.8022115032404498</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.8913367002880466</v>
+        <v>-0.8028051060632306</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.0723162724972846</v>
+        <v>-0.00284657476469081</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.4442795848554182</v>
+        <v>-0.3625860362471851</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.03262017394636575</v>
+        <v>-0.255468666320377</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>46.85387823164994</v>
+        <v>78.46923385032865</v>
       </c>
       <c r="B27" t="n">
-        <v>108.692060112324</v>
+        <v>160.705412590652</v>
       </c>
       <c r="C27" t="n">
-        <v>45.62494910678765</v>
+        <v>45.93858517692269</v>
       </c>
       <c r="D27" t="n">
-        <v>7.532078895087407</v>
+        <v>9.190955587878779</v>
       </c>
       <c r="E27" t="n">
-        <v>2.031938025143852</v>
+        <v>3.318985761976645</v>
       </c>
       <c r="F27" t="n">
-        <v>4.980784936292658</v>
+        <v>9.154028050280042</v>
       </c>
       <c r="G27" t="n">
-        <v>0.301662643206541</v>
+        <v>0.04762695585243399</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.08123633767322978</v>
+        <v>-0.7797278781803736</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5776487665231003</v>
+        <v>-0.8679018672406916</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.3021647266321808</v>
+        <v>-0.8948211122739047</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.02367313676220784</v>
+        <v>-0.002152217106532917</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.5617359218870821</v>
+        <v>-0.4488062725305282</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.002380298780398895</v>
+        <v>-0.09746337264948779</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>68.88603105760475</v>
+        <v>50.0291105644911</v>
       </c>
       <c r="B28" t="n">
-        <v>129.397284571111</v>
+        <v>110.0311626080061</v>
       </c>
       <c r="C28" t="n">
-        <v>45.66648226168225</v>
+        <v>45.61114144068416</v>
       </c>
       <c r="D28" t="n">
-        <v>10.72189323664217</v>
+        <v>7.207806709229352</v>
       </c>
       <c r="E28" t="n">
-        <v>2.156599729226978</v>
+        <v>3.327602453977033</v>
       </c>
       <c r="F28" t="n">
-        <v>7.771220579059301</v>
+        <v>5.410968135709593</v>
       </c>
       <c r="G28" t="n">
-        <v>0.07706266645683511</v>
+        <v>0.2330643583141272</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.6989064808006884</v>
+        <v>-0.1900369682548341</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.8271801409448514</v>
+        <v>-0.6171839620507878</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.8407272878809029</v>
+        <v>-0.4100326065530877</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.1308008767469779</v>
+        <v>-0.0001001558666855797</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.3906143441755903</v>
+        <v>-0.5751892186691923</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.01158677930203441</v>
+        <v>-0.02469809792981476</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>59.23153594062993</v>
+        <v>56.85022149689746</v>
       </c>
       <c r="B29" t="n">
-        <v>165.4372795285038</v>
+        <v>188.6841349134588</v>
       </c>
       <c r="C29" t="n">
-        <v>46.06430937592183</v>
+        <v>45.50006451019897</v>
       </c>
       <c r="D29" t="n">
-        <v>11.06693110878867</v>
+        <v>11.30225566909767</v>
       </c>
       <c r="E29" t="n">
-        <v>2.465632327110021</v>
+        <v>2.548442483538626</v>
       </c>
       <c r="F29" t="n">
-        <v>6.410272212398989</v>
+        <v>6.1216887923517</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1344544159677458</v>
+        <v>0.1553914525344055</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5317582575278839</v>
+        <v>-0.4347754281890714</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.7509272531592088</v>
+        <v>-0.7100403478406949</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.7138026459142478</v>
+        <v>-0.6326096027647269</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.03858239908059647</v>
+        <v>-0.009368951296329692</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.3183501116213493</v>
+        <v>-0.2907172446960626</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.09977144977841858</v>
+        <v>-1.43355997725414e-05</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>82.91463538656976</v>
+        <v>54.48956554289442</v>
       </c>
       <c r="B30" t="n">
-        <v>168.8065319626579</v>
+        <v>155.0627076853021</v>
       </c>
       <c r="C30" t="n">
-        <v>45.6230942362966</v>
+        <v>45.50006300685553</v>
       </c>
       <c r="D30" t="n">
-        <v>8.663378739663351</v>
+        <v>11.48334514089346</v>
       </c>
       <c r="E30" t="n">
-        <v>2.044034310976955</v>
+        <v>2.069740063989769</v>
       </c>
       <c r="F30" t="n">
-        <v>9.845931117657733</v>
+        <v>5.84912172823265</v>
       </c>
       <c r="G30" t="n">
-        <v>0.03952168107855909</v>
+        <v>0.1824182168326272</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.8240939687348593</v>
+        <v>-0.3593887636206228</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.8917070231757631</v>
+        <v>-0.6795571269701776</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.9218900672844494</v>
+        <v>-0.5660803682658159</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.03266229908245907</v>
+        <v>-0.005983936741655067</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.4956189366847649</v>
+        <v>-0.2734549480324153</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.001969137406085828</v>
+        <v>-1.400152345037986e-05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>73.80375633445689</v>
+        <v>60.91713845656678</v>
       </c>
       <c r="B31" t="n">
-        <v>129.3427600137835</v>
+        <v>111.0721546257308</v>
       </c>
       <c r="C31" t="n">
-        <v>45.76136491379481</v>
+        <v>45.51581812845622</v>
       </c>
       <c r="D31" t="n">
-        <v>9.660053504910211</v>
+        <v>11.37535025491738</v>
       </c>
       <c r="E31" t="n">
-        <v>2.561068313851065</v>
+        <v>2.327942133742321</v>
       </c>
       <c r="F31" t="n">
-        <v>8.380761838602142</v>
+        <v>6.70171110529935</v>
       </c>
       <c r="G31" t="n">
-        <v>0.05977517152031977</v>
+        <v>0.1202892247089721</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7538475943050039</v>
+        <v>-0.5384875084923078</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8545488151880331</v>
+        <v>-0.7537643923528076</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.8780977949372892</v>
+        <v>-0.7193112132745733</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.03434986254752401</v>
+        <v>-0.08252484139591505</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.4274236893291736</v>
+        <v>-0.3204565749636445</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.03261901946611871</v>
+        <v>-0.003515139656938837</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>72.49899775044392</v>
+        <v>47.03916407676516</v>
       </c>
       <c r="B32" t="n">
-        <v>98.21827355181402</v>
+        <v>75.8872028976707</v>
       </c>
       <c r="C32" t="n">
-        <v>45.74048915006826</v>
+        <v>45.5021508391111</v>
       </c>
       <c r="D32" t="n">
-        <v>9.653890092327925</v>
+        <v>7.601702229146588</v>
       </c>
       <c r="E32" t="n">
-        <v>2.559253303730432</v>
+        <v>3.413241714363763</v>
       </c>
       <c r="F32" t="n">
-        <v>8.154561436363853</v>
+        <v>5.03219636787227</v>
       </c>
       <c r="G32" t="n">
-        <v>0.06369075778965862</v>
+        <v>0.2946119843305542</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7408271223067618</v>
+        <v>-0.02794480018091465</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8479776710194417</v>
+        <v>-0.5586921552227305</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.8694834220542204</v>
+        <v>-0.2480696661435232</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.005469814829249085</v>
+        <v>-0.01109663339686818</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.4176575258374674</v>
+        <v>-0.5557545664989736</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.02799157634000608</v>
+        <v>-0.0004779642469125711</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>74.76810659877431</v>
+        <v>56.85022149689746</v>
       </c>
       <c r="B33" t="n">
-        <v>129.4895518067116</v>
+        <v>186.3676496231622</v>
       </c>
       <c r="C33" t="n">
-        <v>45.76137012199645</v>
+        <v>45.50006451019897</v>
       </c>
       <c r="D33" t="n">
-        <v>9.61343236228466</v>
+        <v>11.30225566909767</v>
       </c>
       <c r="E33" t="n">
-        <v>2.402826564870957</v>
+        <v>2.548442483538626</v>
       </c>
       <c r="F33" t="n">
-        <v>8.539312193603541</v>
+        <v>6.1216887923517</v>
       </c>
       <c r="G33" t="n">
-        <v>0.05706690224212315</v>
+        <v>0.1553914525344055</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.762920165031559</v>
+        <v>-0.4347754281890714</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8591841712507672</v>
+        <v>-0.7100403478406949</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.8840151170279983</v>
+        <v>-0.6326096027647269</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.04525316763276484</v>
+        <v>-0.009368951296329692</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.4346418846796327</v>
+        <v>-0.2907172446960626</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.03262017394636575</v>
+        <v>-1.43355997725414e-05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>64.93377607322692</v>
+        <v>52.52025126883895</v>
       </c>
       <c r="B34" t="n">
-        <v>162.5837411010582</v>
+        <v>79.97677941611943</v>
       </c>
       <c r="C34" t="n">
-        <v>46.03410214601767</v>
+        <v>45.5127899524914</v>
       </c>
       <c r="D34" t="n">
-        <v>10.41239865737348</v>
+        <v>7.030936342766635</v>
       </c>
       <c r="E34" t="n">
-        <v>2.55544257353541</v>
+        <v>2.395245064204837</v>
       </c>
       <c r="F34" t="n">
-        <v>7.104170866912136</v>
+        <v>5.772837015117407</v>
       </c>
       <c r="G34" t="n">
-        <v>0.09535865412065944</v>
+        <v>0.1941260990885859</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6425480482695661</v>
+        <v>-0.298249858118167</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8005503343675187</v>
+        <v>-0.6580345327608561</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.8000493145995816</v>
+        <v>-0.5124069244710339</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.01529718643796008</v>
+        <v>-0.03229758430634524</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.36103157782227</v>
+        <v>-0.5913816332474531</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.09307553962107734</v>
+        <v>-0.002842211664755429</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>48.85207927849513</v>
+        <v>51.24250991186361</v>
       </c>
       <c r="B35" t="n">
-        <v>85.60202394325917</v>
+        <v>111.3667896037549</v>
       </c>
       <c r="C35" t="n">
-        <v>45.62362572316846</v>
+        <v>45.51660388008566</v>
       </c>
       <c r="D35" t="n">
-        <v>7.645618886056113</v>
+        <v>7.072295510973032</v>
       </c>
       <c r="E35" t="n">
-        <v>2.164579646962616</v>
+        <v>3.314522664424826</v>
       </c>
       <c r="F35" t="n">
-        <v>5.30328693711793</v>
+        <v>5.573169791251998</v>
       </c>
       <c r="G35" t="n">
-        <v>0.257815405715495</v>
+        <v>0.2128750667237744</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.1876850145649891</v>
+        <v>-0.2454191966963242</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6162908970364172</v>
+        <v>-0.6378983352155277</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.4074897838804285</v>
+        <v>-0.4630440604318692</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.1114478675056784</v>
+        <v>-0.0004027331248808978</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.5750306814451763</v>
+        <v>-0.5830763144271134</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.002086949875321168</v>
+        <v>-0.00368975113014619</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>49.78401723603747</v>
+        <v>67.87659778758908</v>
       </c>
       <c r="B36" t="n">
-        <v>85.24477274063443</v>
+        <v>123.1093492592675</v>
       </c>
       <c r="C36" t="n">
-        <v>45.61619151536703</v>
+        <v>45.5002143634075</v>
       </c>
       <c r="D36" t="n">
-        <v>7.104446784569524</v>
+        <v>11.38149765436035</v>
       </c>
       <c r="E36" t="n">
-        <v>2.396344318145127</v>
+        <v>4.128726929129954</v>
       </c>
       <c r="F36" t="n">
-        <v>5.335838456280833</v>
+        <v>7.75814057155824</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2393952212498603</v>
+        <v>0.08094360673666962</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.2322125551274837</v>
+        <v>-0.6635783475544023</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6329752650011763</v>
+        <v>-0.8101964885980627</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.450348518284666</v>
+        <v>-0.8154899350666387</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.002902598932530643</v>
+        <v>-0.1860354093558256</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.5812312042044595</v>
+        <v>-0.3713476213217451</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.0004390401633978904</v>
+        <v>-4.763631277646119e-05</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>80.60175054323284</v>
+        <v>71.49899062322886</v>
       </c>
       <c r="B37" t="n">
-        <v>84.61311625330681</v>
+        <v>106.5721381165446</v>
       </c>
       <c r="C37" t="n">
-        <v>41.53344184091104</v>
+        <v>45.50321718753522</v>
       </c>
       <c r="D37" t="n">
-        <v>9.693092868313693</v>
+        <v>10.10119014558112</v>
       </c>
       <c r="E37" t="n">
-        <v>2.58373469193819</v>
+        <v>2.158961858300373</v>
       </c>
       <c r="F37" t="n">
-        <v>9.616161642587887</v>
+        <v>8.090922515563513</v>
       </c>
       <c r="G37" t="n">
-        <v>0.04384090929972836</v>
+        <v>0.06653898119601982</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.808979700070156</v>
+        <v>-0.7114015460236846</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8833796110487302</v>
+        <v>-0.8333305546238379</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.9128614608152442</v>
+        <v>-0.8495127869387966</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.09853473257287565</v>
+        <v>-0.03518231081473815</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.478306912993727</v>
+        <v>-0.3978363689323611</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.1144786865439743</v>
+        <v>-0.000714930563382038</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>97.42029635027723</v>
+        <v>90.08755801614097</v>
       </c>
       <c r="B38" t="n">
-        <v>80.86735507632807</v>
+        <v>76.06945729041939</v>
       </c>
       <c r="C38" t="n">
-        <v>45.69070841660758</v>
+        <v>45.50189131266042</v>
       </c>
       <c r="D38" t="n">
-        <v>7.513977116973396</v>
+        <v>8.013906768463613</v>
       </c>
       <c r="E38" t="n">
-        <v>2.431422323886826</v>
+        <v>2.067289024200893</v>
       </c>
       <c r="F38" t="n">
-        <v>12.6823138341357</v>
+        <v>11.20207966787724</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02282972530451477</v>
+        <v>0.02944887772419891</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8887117121428556</v>
+        <v>-0.8518378649760954</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9289320545922204</v>
+        <v>-0.9072675615656874</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.9573539461558058</v>
+        <v>-0.9377773094156511</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.2153906881274854</v>
+        <v>-0.02078266146834362</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.6041943147375524</v>
+        <v>-0.5337652679930309</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.01695688961511095</v>
+        <v>-0.0004202917023157782</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>70.35122592672246</v>
+        <v>86.96998021449379</v>
       </c>
       <c r="B39" t="n">
-        <v>137.1557377423458</v>
+        <v>154.0431579699165</v>
       </c>
       <c r="C39" t="n">
-        <v>47.56131264323356</v>
+        <v>45.60381788728454</v>
       </c>
       <c r="D39" t="n">
-        <v>9.661713827702615</v>
+        <v>8.875925527142247</v>
       </c>
       <c r="E39" t="n">
-        <v>2.459670379114772</v>
+        <v>3.418416071537498</v>
       </c>
       <c r="F39" t="n">
-        <v>7.875228860554151</v>
+        <v>10.73235779733453</v>
       </c>
       <c r="G39" t="n">
-        <v>0.07111534641055638</v>
+        <v>0.03331630410004466</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.7170604233176471</v>
+        <v>-0.8360406506913567</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.8361272650148642</v>
+        <v>-0.8982855886772868</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.8533690160826033</v>
+        <v>-0.9288427911210339</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.001677424893417454</v>
+        <v>-0.1278963192331225</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.4015813788549118</v>
+        <v>-0.5109679803184859</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.1983620840507641</v>
+        <v>-0.023070641618788</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>96.15839269322628</v>
+        <v>67.73957474273467</v>
       </c>
       <c r="B40" t="n">
-        <v>98.07429141255666</v>
+        <v>122.7853069011509</v>
       </c>
       <c r="C40" t="n">
-        <v>45.74048915006826</v>
+        <v>46.64960899844169</v>
       </c>
       <c r="D40" t="n">
-        <v>7.236560576965197</v>
+        <v>10.22420843734368</v>
       </c>
       <c r="E40" t="n">
-        <v>2.597190778131834</v>
+        <v>3.380814132447288</v>
       </c>
       <c r="F40" t="n">
-        <v>12.34024324822932</v>
+        <v>7.552174874244812</v>
       </c>
       <c r="G40" t="n">
-        <v>0.02380742370511942</v>
+        <v>0.08103101460514239</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.8846000905080421</v>
+        <v>-0.6621211417270744</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9264732957284991</v>
+        <v>-0.8096614468722004</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9552649279697786</v>
+        <v>-0.8144989296090936</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.10839655810702</v>
+        <v>-0.01402564114153733</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.5947489218682926</v>
+        <v>-0.3703456403062473</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.02799157634000608</v>
+        <v>-0.255468666320377</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>77.18593241643615</v>
+        <v>52.08679282149426</v>
       </c>
       <c r="B41" t="n">
-        <v>85.99575961525029</v>
+        <v>82.50617159367516</v>
       </c>
       <c r="C41" t="n">
-        <v>45.79118126459122</v>
+        <v>45.51301162309813</v>
       </c>
       <c r="D41" t="n">
-        <v>9.99311706207531</v>
+        <v>6.991126196631063</v>
       </c>
       <c r="E41" t="n">
-        <v>2.339979016762258</v>
+        <v>2.395114903413687</v>
       </c>
       <c r="F41" t="n">
-        <v>9.049972809409713</v>
+        <v>5.693466255658975</v>
       </c>
       <c r="G41" t="n">
-        <v>0.05111700017640104</v>
+        <v>0.2001789157255259</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.7835718817513425</v>
+        <v>-0.2809508761878515</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8698395870649264</v>
+        <v>-0.6514055100227245</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.8971875149917461</v>
+        <v>-0.4963830173164853</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.1638481631877313</v>
+        <v>-0.006254929142111146</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.4527393952222567</v>
+        <v>-0.5885641533397126</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.03922828508848554</v>
+        <v>-0.00289147179958496</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>94.59301644875995</v>
+        <v>73.98505433662038</v>
       </c>
       <c r="B42" t="n">
-        <v>80.86735507632807</v>
+        <v>95.75994042741826</v>
       </c>
       <c r="C42" t="n">
-        <v>42.48184792559748</v>
+        <v>45.60508505184268</v>
       </c>
       <c r="D42" t="n">
-        <v>7.512824512570933</v>
+        <v>10.01568816630233</v>
       </c>
       <c r="E42" t="n">
-        <v>2.372947306755533</v>
+        <v>3.324062281807971</v>
       </c>
       <c r="F42" t="n">
-        <v>12.08008587480794</v>
+        <v>8.504103273509527</v>
       </c>
       <c r="G42" t="n">
-        <v>0.02518076851917742</v>
+        <v>0.05887885633477657</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.8790947537332006</v>
+        <v>-0.738640556948111</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.9231584790226022</v>
+        <v>-0.8468147860533254</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.9524215662840457</v>
+        <v>-0.8680438252069689</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.05151784409545344</v>
+        <v>-0.06810307929864821</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.5830320261016659</v>
+        <v>-0.4160157098365365</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.257101691308786</v>
+        <v>-0.02335223374281825</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>46.61327078157298</v>
+        <v>51.56682367270646</v>
       </c>
       <c r="B43" t="n">
-        <v>84.6810537691558</v>
+        <v>103.0258018735222</v>
       </c>
       <c r="C43" t="n">
-        <v>45.61460183836046</v>
+        <v>46.59051142311048</v>
       </c>
       <c r="D43" t="n">
-        <v>7.532078895087407</v>
+        <v>7.154159305291698</v>
       </c>
       <c r="E43" t="n">
-        <v>2.572791198119447</v>
+        <v>2.423021320387399</v>
       </c>
       <c r="F43" t="n">
-        <v>4.945244226905785</v>
+        <v>5.67688484284443</v>
       </c>
       <c r="G43" t="n">
-        <v>0.3075977464157791</v>
+        <v>0.2081900172783701</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.06715733009447072</v>
+        <v>-0.2590949076655134</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5726323092905964</v>
+        <v>-0.6430274763408725</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.2879157272397522</v>
+        <v>-0.4758915792829849</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.01612328038548439</v>
+        <v>-0.055952280182301</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.5601350728625506</v>
+        <v>-0.585184353872592</v>
       </c>
       <c r="M43" t="n">
-        <v>-8.666311826840411e-05</v>
+        <v>-0.2423358718023312</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>49.80508123857206</v>
+        <v>49.02544390625076</v>
       </c>
       <c r="B44" t="n">
-        <v>85.24477274063443</v>
+        <v>106.5721381165446</v>
       </c>
       <c r="C44" t="n">
-        <v>45.61618655337424</v>
+        <v>45.50320223038107</v>
       </c>
       <c r="D44" t="n">
-        <v>7.104446784569524</v>
+        <v>7.504771046295576</v>
       </c>
       <c r="E44" t="n">
-        <v>2.396344318145127</v>
+        <v>3.372694316662297</v>
       </c>
       <c r="F44" t="n">
-        <v>5.339120807553535</v>
+        <v>5.312109798370273</v>
       </c>
       <c r="G44" t="n">
-        <v>0.2390151783814371</v>
+        <v>0.2519016466085992</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.2331691713668294</v>
+        <v>-0.1398338778250215</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.633334430725753</v>
+        <v>-0.5987146893867162</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.4512581880050581</v>
+        <v>-0.3608917835227564</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.003623492550282961</v>
+        <v>-0.0451905444772739</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.5813713506874526</v>
+        <v>-0.5686653853906298</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.0004379402592345464</v>
+        <v>-0.0007116067513475433</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>71.29989564917867</v>
+        <v>97.02639936410515</v>
       </c>
       <c r="B45" t="n">
-        <v>113.5779227185407</v>
+        <v>105.8619289514574</v>
       </c>
       <c r="C45" t="n">
-        <v>45.69708514501968</v>
+        <v>45.50343722246682</v>
       </c>
       <c r="D45" t="n">
-        <v>10.1018841296128</v>
+        <v>7.066798205703164</v>
       </c>
       <c r="E45" t="n">
-        <v>2.569110971050491</v>
+        <v>3.804571847671558</v>
       </c>
       <c r="F45" t="n">
-        <v>8.042393493434188</v>
+        <v>12.5377876359999</v>
       </c>
       <c r="G45" t="n">
-        <v>0.06779878592374483</v>
+        <v>0.02291607373085537</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.727813873166461</v>
+        <v>-0.8799902789571774</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.8414270912187839</v>
+        <v>-0.923723609251852</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.8607063031389537</v>
+        <v>-0.9529059974839561</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.06781106902221032</v>
+        <v>-0.006016985270267871</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.4086822048028381</v>
+        <v>-0.5845055453500188</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.01837039229909412</v>
+        <v>-0.0007638272148485781</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>52.53673011130996</v>
+        <v>90.08755801614097</v>
       </c>
       <c r="B46" t="n">
-        <v>107.0398229788959</v>
+        <v>76.06945729041939</v>
       </c>
       <c r="C46" t="n">
-        <v>46.03189513959843</v>
+        <v>45.50189131266042</v>
       </c>
       <c r="D46" t="n">
-        <v>6.776430326103154</v>
+        <v>8.013906768463613</v>
       </c>
       <c r="E46" t="n">
-        <v>2.141279256562429</v>
+        <v>2.091407050587872</v>
       </c>
       <c r="F46" t="n">
-        <v>5.721945117670505</v>
+        <v>11.20207966787724</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1954444642958961</v>
+        <v>0.02944887772419891</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.3449185950646224</v>
+        <v>-0.8518378649760954</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6762415328677986</v>
+        <v>-0.9072675615656874</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.5548879941003937</v>
+        <v>-0.9377773094156511</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.01663948880835919</v>
+        <v>-0.02078266146834362</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.5995460058441634</v>
+        <v>-0.5337652679930309</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.09258632175016374</v>
+        <v>-0.0004202917023157782</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>53.7230913355245</v>
+        <v>85.71612390247461</v>
       </c>
       <c r="B47" t="n">
-        <v>113.6302840442653</v>
+        <v>121.3282286687597</v>
       </c>
       <c r="C47" t="n">
-        <v>45.62968641132358</v>
+        <v>45.50251065639632</v>
       </c>
       <c r="D47" t="n">
-        <v>11.22057768901617</v>
+        <v>8.596739089666761</v>
       </c>
       <c r="E47" t="n">
-        <v>2.589722971837608</v>
+        <v>3.409439294784174</v>
       </c>
       <c r="F47" t="n">
-        <v>5.762306437608748</v>
+        <v>10.41605902908823</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1930275117843125</v>
+        <v>0.03495839978304084</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.3766697445952311</v>
+        <v>-0.8291743462510486</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.686658454866598</v>
+        <v>-0.8944997827666556</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.581586043505168</v>
+        <v>-0.9248826052312765</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.01721677892211672</v>
+        <v>-0.0360303327571689</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.2991987795569718</v>
+        <v>-0.5017991560368456</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.00343039723898455</v>
+        <v>-0.0005579236436262236</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>89.95339244984299</v>
+        <v>85.71612390247461</v>
       </c>
       <c r="B48" t="n">
-        <v>104.7619009949724</v>
+        <v>104.5706761662165</v>
       </c>
       <c r="C48" t="n">
-        <v>45.62305499835881</v>
+        <v>45.50251065639632</v>
       </c>
       <c r="D48" t="n">
-        <v>7.828843299409007</v>
+        <v>8.596739089666761</v>
       </c>
       <c r="E48" t="n">
-        <v>2.016525545667468</v>
+        <v>3.410191297845851</v>
       </c>
       <c r="F48" t="n">
-        <v>11.10267338750839</v>
+        <v>10.41605902908823</v>
       </c>
       <c r="G48" t="n">
-        <v>0.02981134268121604</v>
+        <v>0.03495839978304084</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.8606337078348141</v>
+        <v>-0.8291743462510486</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9123369846165583</v>
+        <v>-0.8944997827666556</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.9425978018403912</v>
+        <v>-0.9248826052312765</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.03923753878740997</v>
+        <v>-0.0360303327571689</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.5483042787094201</v>
+        <v>-0.5017991560368456</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.001960439696728221</v>
+        <v>-0.0005579236436262236</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>90.21637486171841</v>
+        <v>50.0291105644911</v>
       </c>
       <c r="B49" t="n">
-        <v>109.5863593779582</v>
+        <v>111.0721546257308</v>
       </c>
       <c r="C49" t="n">
-        <v>45.73964801710494</v>
+        <v>45.61114144068416</v>
       </c>
       <c r="D49" t="n">
-        <v>7.948960651630202</v>
+        <v>7.207806709229352</v>
       </c>
       <c r="E49" t="n">
-        <v>2.016525545667468</v>
+        <v>3.399506895723941</v>
       </c>
       <c r="F49" t="n">
-        <v>11.1870960995547</v>
+        <v>5.410968135709593</v>
       </c>
       <c r="G49" t="n">
-        <v>0.02953829543562527</v>
+        <v>0.2330643583141272</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.8617571440810949</v>
+        <v>-0.1900369682548341</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.9129755412142661</v>
+        <v>-0.6171839620507878</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.9432062279455093</v>
+        <v>-0.4100326065530877</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.07843568624898174</v>
+        <v>-0.0001001558666855797</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.5502727112311816</v>
+        <v>-0.5751892186691923</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.02780512591834822</v>
+        <v>-0.02469809792981476</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>99.03563429799098</v>
+        <v>86.96998021449379</v>
       </c>
       <c r="B50" t="n">
-        <v>118.313306770882</v>
+        <v>154.0431579699165</v>
       </c>
       <c r="C50" t="n">
-        <v>45.62392610078507</v>
+        <v>45.60381788728454</v>
       </c>
       <c r="D50" t="n">
-        <v>7.340428116052436</v>
+        <v>8.875925527142247</v>
       </c>
       <c r="E50" t="n">
-        <v>2.053077793907109</v>
+        <v>3.120503365485669</v>
       </c>
       <c r="F50" t="n">
-        <v>13.01687267596708</v>
+        <v>10.73235779733453</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02161565677952365</v>
+        <v>0.03331630410004466</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.8937386906883492</v>
+        <v>-0.8360406506913567</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.9319738003992166</v>
+        <v>-0.8982855886772868</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.9598789877703439</v>
+        <v>-0.9288427911210339</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.234969769968074</v>
+        <v>-0.1278963192331225</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.6162851755948989</v>
+        <v>-0.5109679803184859</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.002153533323736681</v>
+        <v>-0.023070641618788</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>59.25681109796091</v>
+        <v>54.2579150921126</v>
       </c>
       <c r="B51" t="n">
-        <v>159.4452045720422</v>
+        <v>164.1443669068263</v>
       </c>
       <c r="C51" t="n">
-        <v>46.06178543182924</v>
+        <v>45.54797260928168</v>
       </c>
       <c r="D51" t="n">
-        <v>11.06707061398153</v>
+        <v>11.51034978603824</v>
       </c>
       <c r="E51" t="n">
-        <v>2.165106666659537</v>
+        <v>3.707999244438876</v>
       </c>
       <c r="F51" t="n">
-        <v>6.413690148737585</v>
+        <v>5.827454567882899</v>
       </c>
       <c r="G51" t="n">
-        <v>0.134241175406305</v>
+        <v>0.1854242552123431</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.5323439498747452</v>
+        <v>-0.3512447339516773</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.7511803493293258</v>
+        <v>-0.6763183336342152</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.7142779200333161</v>
+        <v>-0.5587257650238049</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.03895370708367978</v>
+        <v>-0.00831000988448727</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.3185392970551894</v>
+        <v>-0.2717610041110734</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.09921197766065935</v>
+        <v>-0.01066057984037277</v>
       </c>
     </row>
   </sheetData>
